--- a/dcf/HDB.xlsx
+++ b/dcf/HDB.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.01943157778424648</v>
+        <v>0.01944472608120765</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.02443157778424648</v>
+        <v>0.02444472608120764</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.02943157778424648</v>
+        <v>0.02944472608120765</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.03443157778424648</v>
+        <v>0.03444472608120765</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.03943157778424648</v>
+        <v>0.03944472608120764</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.04443157778424648</v>
+        <v>0.04444472608120765</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.04943157778424648</v>
+        <v>0.04944472608120765</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>73.44812286866433</v>
+        <v>73.43864043796509</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>69.92938186313451</v>
+        <v>69.92035505845034</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>66.57916359259109</v>
+        <v>66.57056766568833</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>63.38833966867356</v>
+        <v>63.38015134614112</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>60.34832430032446</v>
+        <v>60.34052168850823</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>57.45103940436834</v>
+        <v>57.44360190087558</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>54.68888212150214</v>
+        <v>54.681790332792</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>79.0887118739083</v>
+        <v>79.0785019899874</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>75.30063608071195</v>
+        <v>75.29091993901439</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>71.69516219022968</v>
+        <v>71.6859128741639</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>68.26236274591476</v>
+        <v>68.25355494671203</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>64.99290178711934</v>
+        <v>64.98451170002414</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>61.87799675231895</v>
+        <v>61.87000197996263</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>58.90938301209769</v>
+        <v>58.90176247452526</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>84.72930087915228</v>
+        <v>84.71836354200977</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>80.67189029828938</v>
+        <v>80.66148481957842</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>76.81116078786827</v>
+        <v>76.80125808263948</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>73.13638582315595</v>
+        <v>73.12695854728291</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>69.63747927391421</v>
+        <v>69.62850171154008</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>66.3049541002696</v>
+        <v>66.29640205904968</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>63.12988390269326</v>
+        <v>63.1217346162585</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>90.36988988439627</v>
+        <v>90.35822509403209</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>86.04314451586684</v>
+        <v>86.03204970014247</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>81.92715938550683</v>
+        <v>81.91660329111502</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>78.01040890039712</v>
+        <v>78.00036214785381</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>74.28205676070908</v>
+        <v>74.27249172305601</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>70.73191144822023</v>
+        <v>70.72280213813673</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>67.35038479328881</v>
+        <v>67.34170675799177</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>96.01047888964025</v>
+        <v>95.99808664605442</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>91.41439873344429</v>
+        <v>91.40261458070651</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>87.04315798314542</v>
+        <v>87.03194849959057</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>82.88443197763833</v>
+        <v>82.8737657484247</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>78.92663424750394</v>
+        <v>78.91648173457192</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>75.15886879617084</v>
+        <v>75.14920221722376</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>71.57088568388436</v>
+        <v>71.561678899725</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>101.6510678948843</v>
+        <v>101.6379481980767</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>96.78565295102173</v>
+        <v>96.77317946127056</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>92.15915658078401</v>
+        <v>92.14729370806614</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>87.75845505487952</v>
+        <v>87.74716934899563</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>83.57121173429881</v>
+        <v>83.56047174608783</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>79.58582614412147</v>
+        <v>79.57560229631079</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>75.79138657447993</v>
+        <v>75.78165104145826</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>107.2916569001282</v>
+        <v>107.2778097500991</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>102.1569071685992</v>
+        <v>102.1437443418346</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>97.27515517842257</v>
+        <v>97.2626389165417</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>92.63247813212072</v>
+        <v>92.62057294956652</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>88.21578922109369</v>
+        <v>88.20446175760375</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>84.01278349207207</v>
+        <v>84.00200237539782</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>80.01188746507546</v>
+        <v>80.0016231831915</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>25.77000045776367</v>
+        <v>27.2450008392334</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.03443157778424648</v>
+        <v>0.03444472608120765</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.01113760726503249</v>
+        <v>0.01113754608088853</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>25.77000045776367</v>
+        <v>27.2450008392334</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>78.01040890039712</v>
+        <v>78.00036214785381</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>121.20418197242</v>
+        <v>121.1890873003102</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>47.17591790491117</v>
+        <v>47.16940872583067</v>
       </c>
     </row>
     <row r="59">
